--- a/data/raw/inventory/Week 36/Tonor/Imports (OrderPilot).xlsx
+++ b/data/raw/inventory/Week 36/Tonor/Imports (OrderPilot).xlsx
@@ -1707,7 +1707,7 @@
         <v>83</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1026</v>
       </c>
       <c r="F44" t="s">
         <v>108</v>
